--- a/db/bankstatements/2026-2027/corpus-account/tracking_sheet.xlsx
+++ b/db/bankstatements/2026-2027/corpus-account/tracking_sheet.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Payment Tracking" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="All Transactions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Unmatched Transactions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payment Tracking" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unmatched Transactions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -606,7 +606,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated on 13-Oct-2026 08:06 AM | Source: Bank Statement</t>
+          <t>Generated on 13-Oct-2026 08:13 AM | Source: Bank Statement</t>
         </is>
       </c>
     </row>
@@ -797,25 +797,19 @@
           <t>Renu R</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>PAID</t>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="E8" s="12" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="17" t="n">
-        <v>6500</v>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>4 Oct 2026</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G8" s="14" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr"/>
       <c r="I8" s="14" t="inlineStr"/>
       <c r="J8" s="13" t="inlineStr"/>
       <c r="K8" s="14" t="inlineStr"/>
@@ -1053,19 +1047,25 @@
           <t>Geetha N</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>PAID</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>6500</v>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>4 Oct 2026</t>
+        </is>
+      </c>
       <c r="I15" s="9" t="inlineStr"/>
       <c r="J15" s="8" t="inlineStr"/>
       <c r="K15" s="9" t="inlineStr"/>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Renu R</t>
+          <t>Geetha N</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
